--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_5.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_23_5.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_24</t>
+          <t>model_23_5_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9981531577726562</v>
+        <v>0.9999734985929342</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7098521185186477</v>
+        <v>0.7128537312867349</v>
       </c>
       <c r="D2" t="n">
-        <v>0.992601123164457</v>
+        <v>0.9999966425216926</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9963380315714016</v>
+        <v>0.9998728326112831</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9954632499588023</v>
+        <v>0.9999536121462839</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00109636532558141</v>
+        <v>1.573238003548976e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1722443161831894</v>
+        <v>0.1704624291811327</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003575584745914742</v>
+        <v>1.35515860885475e-06</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00265086448586094</v>
+        <v>3.020660616797506e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.003113230482918626</v>
+        <v>1.578086936894997e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01128689810487991</v>
+        <v>0.001505910833000038</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03311140778616049</v>
+        <v>0.00396640643851456</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000852388720312</v>
+        <v>1.000012231418646</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03452102896568059</v>
+        <v>0.004135264572195362</v>
       </c>
       <c r="P2" t="n">
-        <v>165.6315096394735</v>
+        <v>174.1195790936824</v>
       </c>
       <c r="Q2" t="n">
-        <v>258.2660723294568</v>
+        <v>266.7541417836657</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_23</t>
+          <t>model_23_5_1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9981180860865649</v>
+        <v>0.9999763652652509</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7091674011653979</v>
+        <v>0.7126979881597039</v>
       </c>
       <c r="D3" t="n">
-        <v>0.99261911189737</v>
+        <v>0.9999914909537464</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9963489543467343</v>
+        <v>0.9998729113800128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9954753537704714</v>
+        <v>0.9999505835264647</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001117185393463169</v>
+        <v>1.4030599514451e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.172650793982328</v>
+        <v>0.1705548850290911</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003566891502273648</v>
+        <v>3.434454739000634e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002642957591582307</v>
+        <v>3.018789589941335e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.003104924546927978</v>
+        <v>1.681118765069643e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01143383322108442</v>
+        <v>0.001492366431090801</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03342432338078317</v>
+        <v>0.003745744187000896</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000868575652355</v>
+        <v>1.000010908339115</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03484726602499094</v>
+        <v>0.003905208271800928</v>
       </c>
       <c r="P3" t="n">
-        <v>165.5938855964301</v>
+        <v>174.3485398677365</v>
       </c>
       <c r="Q3" t="n">
-        <v>258.2284482864134</v>
+        <v>266.9831025577198</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_22</t>
+          <t>model_23_5_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9980741591697182</v>
+        <v>0.9999783524915586</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7084018722489305</v>
+        <v>0.7125557326082711</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9926380390478607</v>
+        <v>0.9999846196990997</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9963613286653464</v>
+        <v>0.9998723619411999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9954885450716486</v>
+        <v>0.9999463152760811</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001143262308847436</v>
+        <v>1.285089613447032e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1731052450162705</v>
+        <v>0.1706393340695415</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003557744758506641</v>
+        <v>6.207857583507244e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002633999938782887</v>
+        <v>3.031840641790151e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.003095872348644764</v>
+        <v>1.82632208089998e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01160520010457271</v>
+        <v>0.001483311004409741</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03381216214393034</v>
+        <v>0.003584814658315031</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000888849613976</v>
+        <v>1.000009991157742</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0352516158872222</v>
+        <v>0.003737427639908857</v>
       </c>
       <c r="P4" t="n">
-        <v>165.5477388578871</v>
+        <v>174.5241940219271</v>
       </c>
       <c r="Q4" t="n">
-        <v>258.1823015478704</v>
+        <v>267.1587567119104</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_21</t>
+          <t>model_23_5_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9980192133896731</v>
+        <v>0.9999796647208611</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7075460544741412</v>
+        <v>0.712426119609507</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9926579524311504</v>
+        <v>0.9999766419064884</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9963752117914965</v>
+        <v>0.9998713716755355</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9955028794522248</v>
+        <v>0.9999412369155851</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001175880497416261</v>
+        <v>1.207190013517545e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1736132954167883</v>
+        <v>0.1707162779445978</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003548121407407195</v>
+        <v>9.427885636489324e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002623950074404976</v>
+        <v>3.055362839758417e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003086035740906086</v>
+        <v>1.999084856445415e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01179510822313758</v>
+        <v>0.00147502023257994</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03429111397164374</v>
+        <v>0.003474464006890192</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000914209204766</v>
+        <v>1.000009385513449</v>
       </c>
       <c r="O5" t="n">
-        <v>0.03575095768580833</v>
+        <v>0.003622379132795523</v>
       </c>
       <c r="P5" t="n">
-        <v>165.4914761050249</v>
+        <v>174.6492602179341</v>
       </c>
       <c r="Q5" t="n">
-        <v>258.1260387950082</v>
+        <v>267.2838229079173</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_20</t>
+          <t>model_23_5_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9979506258867182</v>
+        <v>0.9999804621407902</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7065886425372521</v>
+        <v>0.712308090104028</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9926787135184482</v>
+        <v>0.9999680324440113</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9963909224099868</v>
+        <v>0.9998700623356145</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9955184762225453</v>
+        <v>0.9999356730366217</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001216597001996182</v>
+        <v>1.159851721850816e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1741816565005679</v>
+        <v>0.1707863453576594</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003538088394464753</v>
+        <v>1.290287076676676e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002612577305518726</v>
+        <v>3.086464143112374e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.003075332849991739</v>
+        <v>2.188364678795945e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01200538091883457</v>
+        <v>0.001467350416341205</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03487975060111786</v>
+        <v>0.003405659586410268</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000945864975361</v>
+        <v>1.000009017473481</v>
       </c>
       <c r="O6" t="n">
-        <v>0.03636465379524496</v>
+        <v>0.003550645565690983</v>
       </c>
       <c r="P6" t="n">
-        <v>165.4233953206569</v>
+        <v>174.7292665880261</v>
       </c>
       <c r="Q6" t="n">
-        <v>258.0579580106402</v>
+        <v>267.3638292780094</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_19</t>
+          <t>model_23_5_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9978651034076769</v>
+        <v>0.9999808703353384</v>
       </c>
       <c r="C7" t="n">
-        <v>0.705516760066669</v>
+        <v>0.7122008821600575</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9927000142805922</v>
+        <v>0.9999591347313608</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9964088024105581</v>
+        <v>0.999868587451197</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9955353988176391</v>
+        <v>0.999929879454177</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00126736683993386</v>
+        <v>1.135619530155313e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1748179722380178</v>
+        <v>0.1708499886243423</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003527794577998892</v>
+        <v>1.649420056665045e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002599634141358374</v>
+        <v>3.121497694710963e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003063720145210167</v>
+        <v>2.385458875688004e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01223813297886791</v>
+        <v>0.001460366988946587</v>
       </c>
       <c r="M7" t="n">
-        <v>0.03560009606635719</v>
+        <v>0.003369895443712332</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000985336888764</v>
+        <v>1.000008829075998</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03711566585826021</v>
+        <v>0.003513358869396414</v>
       </c>
       <c r="P7" t="n">
-        <v>165.3416277705385</v>
+        <v>174.7714942428153</v>
       </c>
       <c r="Q7" t="n">
-        <v>257.9761904605217</v>
+        <v>267.4060569327985</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_18</t>
+          <t>model_23_5_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9977586250458652</v>
+        <v>0.9999809879300157</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7043154486958667</v>
+        <v>0.712103425174718</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9927214867626809</v>
+        <v>0.9999502083261976</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9964293706543065</v>
+        <v>0.9998669828306488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9955538176612683</v>
+        <v>0.9999240240844545</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001330576995130995</v>
+        <v>1.128638602133284e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1755311225616751</v>
+        <v>0.1709078433007624</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003517417776070697</v>
+        <v>2.009711135130802e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002584744983258764</v>
+        <v>3.159612923338506e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.003051080677545971</v>
+        <v>2.584655038683018e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01249570069210692</v>
+        <v>0.001453873762509479</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0364770749256433</v>
+        <v>0.003359521695321052</v>
       </c>
       <c r="N8" t="n">
-        <v>1.001034480748062</v>
+        <v>1.000008774801531</v>
       </c>
       <c r="O8" t="n">
-        <v>0.03802997952318263</v>
+        <v>0.003502543489059499</v>
       </c>
       <c r="P8" t="n">
-        <v>165.2442851998007</v>
+        <v>174.7838266708926</v>
       </c>
       <c r="Q8" t="n">
-        <v>257.8788478897839</v>
+        <v>267.4183893608758</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_17</t>
+          <t>model_23_5_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9976262211587744</v>
+        <v>0.9999808947440364</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7029691392909037</v>
+        <v>0.7120150583801833</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9927428591547331</v>
+        <v>0.9999414360577992</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9964530764769218</v>
+        <v>0.9998653468729459</v>
       </c>
       <c r="F9" t="n">
-        <v>0.995573836296665</v>
+        <v>0.999918248801417</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001409177662058166</v>
+        <v>1.134170524404851e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1763303499819993</v>
+        <v>0.1709603016472449</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003507089343701304</v>
+        <v>2.363780884842934e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002567584561342365</v>
+        <v>3.198472516617789e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003037343393063144</v>
+        <v>2.781126700730362e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0127804089713269</v>
+        <v>0.001447933457853895</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03753901519829957</v>
+        <v>0.003367744830602299</v>
       </c>
       <c r="N9" t="n">
-        <v>1.001095590234412</v>
+        <v>1.000008817810445</v>
       </c>
       <c r="O9" t="n">
-        <v>0.03913712879176529</v>
+        <v>0.003511116700233905</v>
       </c>
       <c r="P9" t="n">
-        <v>165.129497926257</v>
+        <v>174.77404779343</v>
       </c>
       <c r="Q9" t="n">
-        <v>257.7640606162403</v>
+        <v>267.4086104834133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_16</t>
+          <t>model_23_5_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9974617375885675</v>
+        <v>0.9999806477701694</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7014587120838034</v>
+        <v>0.7119349980017062</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9927634482382032</v>
+        <v>0.9999329441243922</v>
       </c>
       <c r="E10" t="n">
-        <v>0.996480668454456</v>
+        <v>0.9998637089246721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9955956569553026</v>
+        <v>0.9999126387485169</v>
       </c>
       <c r="G10" t="n">
-        <v>0.001506822214653264</v>
+        <v>1.148831960027495e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.177227004819192</v>
+        <v>0.1710078289463372</v>
       </c>
       <c r="I10" t="n">
-        <v>0.003497139453410632</v>
+        <v>2.706535643287988e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002547610988449517</v>
+        <v>3.237379392766982e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.003022369515505129</v>
+        <v>2.971977332688645e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01309512527208563</v>
+        <v>0.001442482852169197</v>
       </c>
       <c r="M10" t="n">
-        <v>0.03881780795785955</v>
+        <v>0.003389442373057101</v>
       </c>
       <c r="N10" t="n">
-        <v>1.001171505728353</v>
+        <v>1.000008931798383</v>
       </c>
       <c r="O10" t="n">
-        <v>0.04047036240656569</v>
+        <v>0.003533737951991112</v>
       </c>
       <c r="P10" t="n">
-        <v>164.9955046786417</v>
+        <v>174.7483594513744</v>
       </c>
       <c r="Q10" t="n">
-        <v>257.630067368625</v>
+        <v>267.3829221413577</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_15</t>
+          <t>model_23_5_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.997257628074375</v>
+        <v>0.9999802952928014</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6997627583125086</v>
+        <v>0.7118624111959866</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9927824759770782</v>
+        <v>0.9999248322552183</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9965132157679705</v>
+        <v>0.999862091813594</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9956195237527725</v>
+        <v>0.9999072623415919</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00162799043934985</v>
+        <v>1.16975653920863e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1782337962392209</v>
+        <v>0.1710509196097991</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003487944099253066</v>
+        <v>3.03395009957354e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002524050294470895</v>
+        <v>3.275791314220258e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.003005991526694166</v>
+        <v>3.154879468831576e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01344294804329889</v>
+        <v>0.00143754080169463</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0403483635275317</v>
+        <v>0.003420170374716192</v>
       </c>
       <c r="N11" t="n">
-        <v>1.001265710119519</v>
+        <v>1.000009094480246</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04206607689552559</v>
+        <v>0.003565774108296563</v>
       </c>
       <c r="P11" t="n">
-        <v>164.8408177681085</v>
+        <v>174.7122596479199</v>
       </c>
       <c r="Q11" t="n">
-        <v>257.4753804580918</v>
+        <v>267.3468223379032</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_14</t>
+          <t>model_23_5_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9970045306044815</v>
+        <v>0.999979873954249</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6978570188075901</v>
+        <v>0.7117968154692608</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9927989949647555</v>
+        <v>0.9999171507075902</v>
       </c>
       <c r="E12" t="n">
-        <v>0.996551851447713</v>
+        <v>0.9998605504013235</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9956457030707074</v>
+        <v>0.9999021673013314</v>
       </c>
       <c r="G12" t="n">
-        <v>0.001778240030720042</v>
+        <v>1.194769015766625e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1793651255330005</v>
+        <v>0.1710898600667714</v>
       </c>
       <c r="I12" t="n">
-        <v>0.00347996112539503</v>
+        <v>3.343995748258653e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.002496082289472048</v>
+        <v>3.312405129966821e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.002988026628942046</v>
+        <v>3.328209679953217e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01382680528152507</v>
+        <v>0.001432890136302942</v>
       </c>
       <c r="M12" t="n">
-        <v>0.04216918342486657</v>
+        <v>0.003456543093564183</v>
       </c>
       <c r="N12" t="n">
-        <v>1.001382524336393</v>
+        <v>1.000009288944193</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04396441286550681</v>
+        <v>0.003603695289087821</v>
       </c>
       <c r="P12" t="n">
-        <v>164.6642623011944</v>
+        <v>174.6699451810312</v>
       </c>
       <c r="Q12" t="n">
-        <v>257.2988249911776</v>
+        <v>267.3045078710145</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_13</t>
+          <t>model_23_5_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9966909286977862</v>
+        <v>0.9999794066273933</v>
       </c>
       <c r="C13" t="n">
-        <v>0.695714018499372</v>
+        <v>0.7117373540891324</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9928118153886289</v>
+        <v>0.9999099111740619</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9965979206466125</v>
+        <v>0.9998590626810387</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9956745244695958</v>
+        <v>0.999897353505818</v>
       </c>
       <c r="G13" t="n">
-        <v>0.001964407669431375</v>
+        <v>1.222511556673894e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1806373030887519</v>
+        <v>0.1711251589106135</v>
       </c>
       <c r="I13" t="n">
-        <v>0.003473765521243631</v>
+        <v>3.63620064987884e-05</v>
       </c>
       <c r="J13" t="n">
-        <v>0.002462733229905907</v>
+        <v>3.347743577333849e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002968248669661712</v>
+        <v>3.491972113606344e-05</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01425083172296809</v>
+        <v>0.001428863048662206</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04432163883963875</v>
+        <v>0.003496443273776788</v>
       </c>
       <c r="N13" t="n">
-        <v>1.001527263677945</v>
+        <v>1.000009504633511</v>
       </c>
       <c r="O13" t="n">
-        <v>0.04620850276348281</v>
+        <v>0.003645294102576836</v>
       </c>
       <c r="P13" t="n">
-        <v>164.4651290391923</v>
+        <v>174.6240361386721</v>
       </c>
       <c r="Q13" t="n">
-        <v>257.0996917291756</v>
+        <v>267.2585988286554</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9963026264137858</v>
+        <v>0.9999789178106697</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6933016547629347</v>
+        <v>0.7116836941134084</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9928190455671101</v>
+        <v>0.999903162895098</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9966536425854863</v>
+        <v>0.9998576446304377</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9957064595100956</v>
+        <v>0.9998928544811033</v>
       </c>
       <c r="G14" t="n">
-        <v>0.002194920678999278</v>
+        <v>1.251529828963387e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1820693864113884</v>
+        <v>0.1711570137901935</v>
       </c>
       <c r="I14" t="n">
-        <v>0.003470271461744859</v>
+        <v>3.908577341429248e-05</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00242239664270589</v>
+        <v>3.381427131320295e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.002946334052225374</v>
+        <v>3.645026233645746e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01471844406582816</v>
+        <v>0.001425147210261171</v>
       </c>
       <c r="M14" t="n">
-        <v>0.04684998056562326</v>
+        <v>0.003537696749247152</v>
       </c>
       <c r="N14" t="n">
-        <v>1.001706480116714</v>
+        <v>1.000009730241229</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04884448123113138</v>
+        <v>0.003688303823904441</v>
       </c>
       <c r="P14" t="n">
-        <v>164.2432187404763</v>
+        <v>174.5771175975907</v>
       </c>
       <c r="Q14" t="n">
-        <v>256.8777814304595</v>
+        <v>267.2116802875739</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_11</t>
+          <t>model_23_5_13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9958220996382496</v>
+        <v>0.9999784240161513</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6905840991259253</v>
+        <v>0.7116352181245698</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9928188606892133</v>
+        <v>0.9998968849092049</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9967212612069931</v>
+        <v>0.9998563403083753</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9957420594608442</v>
+        <v>0.9998886777477598</v>
       </c>
       <c r="G15" t="n">
-        <v>0.00248018213063339</v>
+        <v>1.280843604650869e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1836826448298082</v>
+        <v>0.1711857912312218</v>
       </c>
       <c r="I15" t="n">
-        <v>0.003470360805925362</v>
+        <v>4.161971878947381e-05</v>
       </c>
       <c r="J15" t="n">
-        <v>0.002373448158897161</v>
+        <v>3.412409243362981e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.002921904482411261</v>
+        <v>3.787116194708437e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01523395070262028</v>
+        <v>0.00142176890770467</v>
       </c>
       <c r="M15" t="n">
-        <v>0.04980142699394657</v>
+        <v>0.003578887543149225</v>
       </c>
       <c r="N15" t="n">
-        <v>1.001928261705423</v>
+        <v>1.000009958146392</v>
       </c>
       <c r="O15" t="n">
-        <v>0.05192157684424478</v>
+        <v>0.003731248195179622</v>
       </c>
       <c r="P15" t="n">
-        <v>163.9988465634606</v>
+        <v>174.5308130759878</v>
       </c>
       <c r="Q15" t="n">
-        <v>256.6334092534438</v>
+        <v>267.1653757659711</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_10</t>
+          <t>model_23_5_14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9952276802994194</v>
+        <v>0.9999779339368524</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6875194114154652</v>
+        <v>0.7115914114239431</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9928084315696474</v>
+        <v>0.9998910781798508</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9968038712405168</v>
+        <v>0.9998551048323788</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9957819750494308</v>
+        <v>0.9998847995339579</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002833055127741467</v>
+        <v>1.309936828871373e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1855019758423531</v>
+        <v>0.1712117967810647</v>
       </c>
       <c r="I16" t="n">
-        <v>0.003475400787217417</v>
+        <v>4.396345374565472e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.002313647533000541</v>
+        <v>3.441756025767486e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002894513414796047</v>
+        <v>3.91905070016648e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01580194519309341</v>
+        <v>0.001418633570040701</v>
       </c>
       <c r="M16" t="n">
-        <v>0.05322645139159164</v>
+        <v>0.003619304945526659</v>
       </c>
       <c r="N16" t="n">
-        <v>1.002202609092576</v>
+        <v>1.000010184336837</v>
       </c>
       <c r="O16" t="n">
-        <v>0.05549241162127551</v>
+        <v>0.00377338625005182</v>
       </c>
       <c r="P16" t="n">
-        <v>163.7327991983677</v>
+        <v>174.485893102311</v>
       </c>
       <c r="Q16" t="n">
-        <v>256.367361888351</v>
+        <v>267.1204557922943</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_9</t>
+          <t>model_23_5_15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9944927386482927</v>
+        <v>0.9999774561513439</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6840602367391281</v>
+        <v>0.7115518092931452</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9927844119819035</v>
+        <v>0.9998857136236637</v>
       </c>
       <c r="E17" t="n">
-        <v>0.996905037682467</v>
+        <v>0.9998539647809759</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9958268613792793</v>
+        <v>0.9998812191290692</v>
       </c>
       <c r="G17" t="n">
-        <v>0.003269348239676553</v>
+        <v>1.338300240578889e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1875554913587922</v>
+        <v>0.1712353063166293</v>
       </c>
       <c r="I17" t="n">
-        <v>0.003487008504638519</v>
+        <v>4.612871702780883e-05</v>
       </c>
       <c r="J17" t="n">
-        <v>0.002240414097662294</v>
+        <v>3.46883614755767e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.002863711301150406</v>
+        <v>4.040853925169276e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01642746771754525</v>
+        <v>0.001415877637622478</v>
       </c>
       <c r="M17" t="n">
-        <v>0.05717821472970762</v>
+        <v>0.003658278612378899</v>
       </c>
       <c r="N17" t="n">
-        <v>1.002541812931557</v>
+        <v>1.000010404853226</v>
       </c>
       <c r="O17" t="n">
-        <v>0.05961240970597292</v>
+        <v>0.003814019106588574</v>
       </c>
       <c r="P17" t="n">
-        <v>163.446329258045</v>
+        <v>174.443050266771</v>
       </c>
       <c r="Q17" t="n">
-        <v>256.0808919480282</v>
+        <v>267.0776129567543</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_8</t>
+          <t>model_23_5_16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.993584175052771</v>
+        <v>0.999976996778105</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6801528861842996</v>
+        <v>0.7115161596068259</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9927428550068896</v>
+        <v>0.9998807815633353</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9970284503343066</v>
+        <v>0.9998529089653122</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9958773208652398</v>
+        <v>0.9998779254854071</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003808710837881949</v>
+        <v>1.365570620428967e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1898750634368937</v>
+        <v>0.1712564695104147</v>
       </c>
       <c r="I18" t="n">
-        <v>0.003507091348190113</v>
+        <v>4.811941462928658e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.002151076840324709</v>
+        <v>3.493915382305688e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.002829084749451928</v>
+        <v>4.152901705388606e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01711615030739157</v>
+        <v>0.001413303063470167</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06171475381042971</v>
+        <v>0.003695362797383995</v>
       </c>
       <c r="N18" t="n">
-        <v>1.002961149975644</v>
+        <v>1.000010616871644</v>
       </c>
       <c r="O18" t="n">
-        <v>0.06434207864729187</v>
+        <v>0.003852682042124183</v>
       </c>
       <c r="P18" t="n">
-        <v>163.1409290197235</v>
+        <v>174.4027061734842</v>
       </c>
       <c r="Q18" t="n">
-        <v>255.7754917097068</v>
+        <v>267.0372688634675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_7</t>
+          <t>model_23_5_17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9924612543725893</v>
+        <v>0.9999765597679</v>
       </c>
       <c r="C19" t="n">
-        <v>0.675735387479223</v>
+        <v>0.7114839529491049</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9926784267622315</v>
+        <v>0.9998762604508354</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9971786041371961</v>
+        <v>0.9998519357161371</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9959338334022322</v>
+        <v>0.9998749014048623</v>
       </c>
       <c r="G19" t="n">
-        <v>0.004475325061285423</v>
+        <v>1.391513433985017e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1924974814942351</v>
+        <v>0.171275588773693</v>
       </c>
       <c r="I19" t="n">
-        <v>0.00353822697241066</v>
+        <v>4.994424385077518e-05</v>
       </c>
       <c r="J19" t="n">
-        <v>0.00204238191537998</v>
+        <v>3.517033380427157e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00279030444389532</v>
+        <v>4.255779110172806e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>0.01787427450435951</v>
+        <v>0.001411057958009726</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06689787037929849</v>
+        <v>0.003730299497339345</v>
       </c>
       <c r="N19" t="n">
-        <v>1.003479421058805</v>
+        <v>1.000010818568662</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06974585121902782</v>
+        <v>0.00388910606972557</v>
       </c>
       <c r="P19" t="n">
-        <v>162.8183525810001</v>
+        <v>174.3650670174279</v>
       </c>
       <c r="Q19" t="n">
-        <v>255.4529152709833</v>
+        <v>266.9996297074111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_6</t>
+          <t>model_23_5_18</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9910732702891838</v>
+        <v>0.9999761473906952</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6707344286293543</v>
+        <v>0.7114549376041928</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9925842234425658</v>
+        <v>0.9998721205092661</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9973602992393207</v>
+        <v>0.9998510448132892</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9959964970008938</v>
+        <v>0.9998721347732673</v>
       </c>
       <c r="G20" t="n">
-        <v>0.005299292370985362</v>
+        <v>1.415993926243934e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.195466266697691</v>
+        <v>0.1712928135358306</v>
       </c>
       <c r="I20" t="n">
-        <v>0.003583751713570443</v>
+        <v>5.161522336106323e-05</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001910854540726624</v>
+        <v>3.538195371509035e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.002747303127148533</v>
+        <v>4.349898256232638e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.01870918793600934</v>
+        <v>0.001408991356973214</v>
       </c>
       <c r="M20" t="n">
-        <v>0.07279623871454735</v>
+        <v>0.003762969474024383</v>
       </c>
       <c r="N20" t="n">
-        <v>1.0041200290973</v>
+        <v>1.000011008896602</v>
       </c>
       <c r="O20" t="n">
-        <v>0.07589532530561391</v>
+        <v>0.003923166874954265</v>
       </c>
       <c r="P20" t="n">
-        <v>162.4803639644928</v>
+        <v>174.3301875181673</v>
       </c>
       <c r="Q20" t="n">
-        <v>255.1149266544761</v>
+        <v>266.9647502081506</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_5</t>
+          <t>model_23_5_19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9893577162815322</v>
+        <v>0.9999757594310779</v>
       </c>
       <c r="C21" t="n">
-        <v>0.665068241187647</v>
+        <v>0.7114287406679255</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9924516844513238</v>
+        <v>0.9998683351100289</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9975774885948647</v>
+        <v>0.9998502134383007</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9960643840789961</v>
+        <v>0.9998696000875987</v>
       </c>
       <c r="G21" t="n">
-        <v>0.006317719338001701</v>
+        <v>1.439024885024147e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1988299603296411</v>
+        <v>0.1713083651688475</v>
       </c>
       <c r="I21" t="n">
-        <v>0.003647802569647312</v>
+        <v>5.314310109983566e-05</v>
       </c>
       <c r="J21" t="n">
-        <v>0.00175363321002853</v>
+        <v>3.557943372241687e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.002700717329159798</v>
+        <v>4.436126741112627e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01962873077688243</v>
+        <v>0.001407140834261632</v>
       </c>
       <c r="M21" t="n">
-        <v>0.07948408229325983</v>
+        <v>0.003793448147825599</v>
       </c>
       <c r="N21" t="n">
-        <v>1.004911823254677</v>
+        <v>1.000011187954887</v>
       </c>
       <c r="O21" t="n">
-        <v>0.08286788423121692</v>
+        <v>0.003954943088998752</v>
       </c>
       <c r="P21" t="n">
-        <v>162.1287940003816</v>
+        <v>174.2979194878771</v>
       </c>
       <c r="Q21" t="n">
-        <v>254.7633566903648</v>
+        <v>266.9324821778603</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_4</t>
+          <t>model_23_5_20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9872367233909165</v>
+        <v>0.9999753987419534</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6586407970000208</v>
+        <v>0.7114051212763576</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9922699911106778</v>
+        <v>0.9998648829152493</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9978331610541313</v>
+        <v>0.9998494756289579</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9961352584704342</v>
+        <v>0.9998672956381633</v>
       </c>
       <c r="G22" t="n">
-        <v>0.007576832339993381</v>
+        <v>1.460436949547381e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2026455688505479</v>
+        <v>0.1713223866599868</v>
       </c>
       <c r="I22" t="n">
-        <v>0.003735607780044551</v>
+        <v>5.453648954401586e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001568554322676694</v>
+        <v>3.57546886873245e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.002652081562613392</v>
+        <v>4.514522727547406e-05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.02064228762558016</v>
+        <v>0.001405451565856858</v>
       </c>
       <c r="M22" t="n">
-        <v>0.08704500180937089</v>
+        <v>0.003821566366749871</v>
       </c>
       <c r="N22" t="n">
-        <v>1.005890743050346</v>
+        <v>1.000011354426791</v>
       </c>
       <c r="O22" t="n">
-        <v>0.09075068774438992</v>
+        <v>0.003984258358715367</v>
       </c>
       <c r="P22" t="n">
-        <v>161.7653201275394</v>
+        <v>174.2683795870271</v>
       </c>
       <c r="Q22" t="n">
-        <v>254.3998828175226</v>
+        <v>266.9029422770104</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_3</t>
+          <t>model_23_5_21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9846136690062427</v>
+        <v>0.9999750635985373</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6513378238033245</v>
+        <v>0.7113838618132847</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9920237721693744</v>
+        <v>0.9998617472019952</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9981284676648116</v>
+        <v>0.9998487783033698</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9962043253196559</v>
+        <v>0.9998651905810976</v>
       </c>
       <c r="G23" t="n">
-        <v>0.009133990732785239</v>
+        <v>1.480332510472783e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2069809292121225</v>
+        <v>0.1713350071956279</v>
       </c>
       <c r="I23" t="n">
-        <v>0.003854595662968952</v>
+        <v>5.580213846923612e-05</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001354784646079046</v>
+        <v>3.592032737520908e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.002604686176400022</v>
+        <v>4.586135505263004e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.02176068149840761</v>
+        <v>0.001403903637615181</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0955719139328351</v>
+        <v>0.003847508947972419</v>
       </c>
       <c r="N23" t="n">
-        <v>1.00710138353558</v>
+        <v>1.000011509108367</v>
       </c>
       <c r="O23" t="n">
-        <v>0.09964060817009145</v>
+        <v>0.004011305369329105</v>
       </c>
       <c r="P23" t="n">
-        <v>161.3915051576087</v>
+        <v>174.2413174663804</v>
       </c>
       <c r="Q23" t="n">
-        <v>254.0260678475919</v>
+        <v>266.8758801563636</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_2</t>
+          <t>model_23_5_22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9813682736728705</v>
+        <v>0.999974751814626</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6430267636708373</v>
+        <v>0.7113647043082628</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9916937128509721</v>
+        <v>0.9998588798155973</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9984598433704904</v>
+        <v>0.9998481410038997</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9962628827871772</v>
+        <v>0.9998632681662915</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0110605975964536</v>
+        <v>1.498841350282801e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2119147335258708</v>
+        <v>0.17134637991817</v>
       </c>
       <c r="I24" t="n">
-        <v>0.004014100286489289</v>
+        <v>5.695948425268193e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.001114904891026793</v>
+        <v>3.607170780613889e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.002564502588758041</v>
+        <v>4.651534902945327e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.02299640208893998</v>
+        <v>0.001402554713187923</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1051693757538457</v>
+        <v>0.003871487246889496</v>
       </c>
       <c r="N24" t="n">
-        <v>1.008599258304829</v>
+        <v>1.000011653008634</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1096466538103073</v>
+        <v>0.004036304474073004</v>
       </c>
       <c r="P24" t="n">
-        <v>161.0087325042371</v>
+        <v>174.2164661769741</v>
       </c>
       <c r="Q24" t="n">
-        <v>253.6432951942204</v>
+        <v>266.8510288669574</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_1</t>
+          <t>model_23_5_23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9773507564048179</v>
+        <v>0.999974466323505</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6335458360896641</v>
+        <v>0.7113474519628693</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9912524276936512</v>
+        <v>0.9998562857224395</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9988183692626584</v>
+        <v>0.99984757511023</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9962966023541042</v>
+        <v>0.9998615297629231</v>
       </c>
       <c r="G25" t="n">
-        <v>0.01344556939447906</v>
+        <v>1.515789336482607e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2175430216928015</v>
+        <v>0.1713566216556581</v>
       </c>
       <c r="I25" t="n">
-        <v>0.004227355961936568</v>
+        <v>5.800652234294602e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0008553713714619227</v>
+        <v>3.620612691615155e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.002541363384994412</v>
+        <v>4.710674341976542e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.02437574717350116</v>
+        <v>0.001401348708474317</v>
       </c>
       <c r="M25" t="n">
-        <v>0.115955031777319</v>
+        <v>0.003893313930936737</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01045349704393</v>
+        <v>1.000011784773767</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1208914775400858</v>
+        <v>0.004059060365247601</v>
       </c>
       <c r="P25" t="n">
-        <v>160.6182112805051</v>
+        <v>174.1939782950194</v>
       </c>
       <c r="Q25" t="n">
-        <v>253.2527739704884</v>
+        <v>266.8285409850027</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_23_5_0</t>
+          <t>model_23_5_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9723737950100104</v>
+        <v>0.9999742029765372</v>
       </c>
       <c r="C26" t="n">
-        <v>0.622699445076872</v>
+        <v>0.7113319156264252</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9906622691690583</v>
+        <v>0.999853921981992</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9991851400666654</v>
+        <v>0.9998470589354367</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9962822492448683</v>
+        <v>0.999859949296329</v>
       </c>
       <c r="G26" t="n">
-        <v>0.01640010867197456</v>
+        <v>1.531422750092467e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2239819079376902</v>
+        <v>0.1713658446961061</v>
       </c>
       <c r="I26" t="n">
-        <v>0.004512556251806115</v>
+        <v>5.896058456563046e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0005898694378024351</v>
+        <v>3.63287360917618e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.002551212844804275</v>
+        <v>4.764440866757865e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.02602527275773804</v>
+        <v>0.001400240165764738</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1280629090407311</v>
+        <v>0.003913339686370794</v>
       </c>
       <c r="N26" t="n">
-        <v>1.012750556149226</v>
+        <v>1.000011906318521</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1335148122053625</v>
+        <v>0.004079938658549515</v>
       </c>
       <c r="P26" t="n">
-        <v>160.220934635668</v>
+        <v>174.1734565192714</v>
       </c>
       <c r="Q26" t="n">
-        <v>252.8554973256513</v>
+        <v>266.8080192092547</v>
       </c>
     </row>
   </sheetData>
